--- a/resources/tool_obs_water_point_iphra_v2.xlsx
+++ b/resources/tool_obs_water_point_iphra_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE617033-0784-4508-9F74-196EC0F24E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C29E65-E940-4A4A-97ED-6153A1F67D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="1" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">survey!$B$1:$M$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">survey!$B$1:$M$118</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -104,7 +104,7 @@
     <author>tc={ACB7281F-A5FF-4C05-9A6A-08303A5049D9}</author>
   </authors>
   <commentList>
-    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{ACB7281F-A5FF-4C05-9A6A-08303A5049D9}">
+    <comment ref="B33" authorId="0" shapeId="0" xr:uid="{ACB7281F-A5FF-4C05-9A6A-08303A5049D9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="429">
   <si>
     <t>type</t>
   </si>
@@ -1254,9 +1254,6 @@
     <t>note_kii</t>
   </si>
   <si>
-    <t>gp_intro_kii</t>
-  </si>
-  <si>
     <t>&lt;span style="color:blue"&gt;Is there any WASH NGO or service provider staff member who can tell you about water quality results or rehabilitation needs for this water point? &lt;/span&gt;</t>
   </si>
   <si>
@@ -1315,9 +1312,6 @@
     <t>gp_test_results</t>
   </si>
   <si>
-    <t>functionality_quality_flow</t>
-  </si>
-  <si>
     <t>note_flow_rate_1</t>
   </si>
   <si>
@@ -1327,14 +1321,164 @@
     <t>indicator_code</t>
   </si>
   <si>
-    <t>44102, 44103</t>
+    <t>13504, 13505</t>
+  </si>
+  <si>
+    <t>13502, 13506</t>
+  </si>
+  <si>
+    <t>label::French (fr)</t>
+  </si>
+  <si>
+    <t>yes_no_dnk</t>
+  </si>
+  <si>
+    <t>Oui</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>Don't know</t>
+  </si>
+  <si>
+    <t>Ne sait pas</t>
+  </si>
+  <si>
+    <t>yes_no_dnk_pnta</t>
+  </si>
+  <si>
+    <t>prefer_not_to_answer</t>
+  </si>
+  <si>
+    <t>Decline to answer</t>
+  </si>
+  <si>
+    <t>Préfère ne pas répondre</t>
+  </si>
+  <si>
+    <t>yes_no_other</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Autre</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>male</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Homme</t>
+  </si>
+  <si>
+    <t>female</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Femme</t>
+  </si>
+  <si>
+    <t>enum_id</t>
+  </si>
+  <si>
+    <t>Team 1</t>
+  </si>
+  <si>
+    <t>Équipe 1</t>
+  </si>
+  <si>
+    <t>Team 2</t>
+  </si>
+  <si>
+    <t>Équipe 2</t>
+  </si>
+  <si>
+    <t>Team 3</t>
+  </si>
+  <si>
+    <t>Équipe 3</t>
+  </si>
+  <si>
+    <t>Team 4</t>
+  </si>
+  <si>
+    <t>Équipe 4</t>
+  </si>
+  <si>
+    <t>Team 5</t>
+  </si>
+  <si>
+    <t>Équipe 5</t>
+  </si>
+  <si>
+    <t>admin1</t>
+  </si>
+  <si>
+    <t>admin1a</t>
+  </si>
+  <si>
+    <t>To be updated by country</t>
+  </si>
+  <si>
+    <t>À mettre à jour par le pays</t>
+  </si>
+  <si>
+    <t>admin1b</t>
+  </si>
+  <si>
+    <t>admin1c</t>
+  </si>
+  <si>
+    <t>admin2</t>
+  </si>
+  <si>
+    <t>admin2a</t>
+  </si>
+  <si>
+    <t>admin2b</t>
+  </si>
+  <si>
+    <t>admin2c</t>
+  </si>
+  <si>
+    <t>admin3</t>
+  </si>
+  <si>
+    <t>admin3a</t>
+  </si>
+  <si>
+    <t>admin3b</t>
+  </si>
+  <si>
+    <t>admin3c</t>
+  </si>
+  <si>
+    <t>admin4</t>
+  </si>
+  <si>
+    <t>admin4a</t>
+  </si>
+  <si>
+    <t>admin4b</t>
+  </si>
+  <si>
+    <t>admin4c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1367,8 +1511,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1417,6 +1567,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1430,7 +1586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1467,11 +1623,66 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1874,7 +2085,7 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B4" dT="2025-07-09T10:14:10.04" personId="{A9E24A12-962C-4CD7-9795-7036DFAD00E1}" id="{ACB7281F-A5FF-4C05-9A6A-08303A5049D9}">
+  <threadedComment ref="B33" dT="2025-07-09T10:14:10.04" personId="{A9E24A12-962C-4CD7-9795-7036DFAD00E1}" id="{ACB7281F-A5FF-4C05-9A6A-08303A5049D9}">
     <text>Proposing these changes to source types, because previous options did not unable to easily classify improved vs. unimproved facilities. Please let me know what you think.</text>
   </threadedComment>
 </ThreadedComments>
@@ -1882,7 +2093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D2A72A4-B69F-42B0-BA64-020C51FE6931}">
-  <dimension ref="A1:M201"/>
+  <dimension ref="A1:M198"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.5703125" style="2" customWidth="1"/>
@@ -1898,7 +2109,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2225,8 +2436,8 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>42002</v>
+      <c r="A19" s="18">
+        <v>13302</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>63</v>
@@ -2245,8 +2456,8 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>42002</v>
+      <c r="A20" s="18">
+        <v>13302</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>27</v>
@@ -2265,8 +2476,8 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>42002</v>
+      <c r="A21" s="18">
+        <v>13302</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>66</v>
@@ -2285,8 +2496,8 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>42002</v>
+      <c r="A22" s="18">
+        <v>13302</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>27</v>
@@ -2305,8 +2516,8 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>42002</v>
+      <c r="A23" s="18">
+        <v>13302</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>67</v>
@@ -2325,8 +2536,8 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>42002</v>
+      <c r="A24" s="18">
+        <v>13302</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>27</v>
@@ -2348,8 +2559,8 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>42002</v>
+      <c r="A25" s="18">
+        <v>13302</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>72</v>
@@ -2368,8 +2579,8 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>42002</v>
+      <c r="A26" s="18">
+        <v>13302</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>27</v>
@@ -2388,8 +2599,8 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>43101</v>
+      <c r="A27" s="18">
+        <v>13402</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>23</v>
@@ -2405,8 +2616,8 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>43101</v>
+      <c r="A28" s="18">
+        <v>13402</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>24</v>
@@ -2422,8 +2633,8 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>43101</v>
+      <c r="A29" s="18">
+        <v>13402</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>23</v>
@@ -2439,8 +2650,8 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>43101</v>
+      <c r="A30" s="18">
+        <v>13402</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>24</v>
@@ -2453,8 +2664,8 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>43201</v>
+      <c r="A31" s="18">
+        <v>13403</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>125</v>
@@ -2473,8 +2684,8 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>43301</v>
+      <c r="A32" s="18">
+        <v>13404</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>34</v>
@@ -2493,8 +2704,8 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>43301</v>
+      <c r="A33" s="18">
+        <v>13404</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>27</v>
@@ -2513,8 +2724,8 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>43302</v>
+      <c r="A34" s="18">
+        <v>13405</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>34</v>
@@ -2533,8 +2744,8 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>43302</v>
+      <c r="A35" s="18">
+        <v>13405</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>27</v>
@@ -2553,8 +2764,8 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>45101</v>
+      <c r="A36" s="18">
+        <v>13601</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>34</v>
@@ -2573,8 +2784,8 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>45101</v>
+      <c r="A37" s="18">
+        <v>13601</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>27</v>
@@ -2593,8 +2804,8 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>45102</v>
+      <c r="A38" s="18">
+        <v>13602</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>34</v>
@@ -2613,8 +2824,8 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>45102</v>
+      <c r="A39" s="18">
+        <v>13602</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>27</v>
@@ -2633,8 +2844,8 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>42101</v>
+      <c r="A40" s="18">
+        <v>13304</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>125</v>
@@ -2653,8 +2864,8 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>42101</v>
+      <c r="A41" s="18">
+        <v>13304</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>34</v>
@@ -2673,8 +2884,8 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>42101</v>
+      <c r="A42" s="18">
+        <v>13304</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>27</v>
@@ -2689,12 +2900,12 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>44301</v>
+      <c r="A43" s="18">
+        <v>13507</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>34</v>
@@ -2713,8 +2924,8 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>43401</v>
+      <c r="A44" s="18">
+        <v>13406</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>34</v>
@@ -2730,8 +2941,8 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>43401</v>
+      <c r="A45" s="18">
+        <v>13406</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>27</v>
@@ -2746,49 +2957,49 @@
         <v>1</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>43402</v>
+      <c r="A46" s="18">
+        <v>13407</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F46" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>43402</v>
+      <c r="A47" s="18">
+        <v>13407</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C47" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="F47" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D47" s="11" t="s">
-        <v>374</v>
-      </c>
-      <c r="F47" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>370</v>
-      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>44301</v>
+      <c r="A48" s="18">
+        <v>13507</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>34</v>
@@ -2810,8 +3021,8 @@
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>44301</v>
+      <c r="A49" s="18">
+        <v>13507</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>265</v>
@@ -2830,8 +3041,8 @@
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>44301</v>
+      <c r="A50" s="18">
+        <v>13507</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>34</v>
@@ -2850,8 +3061,8 @@
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>44301</v>
+      <c r="A51" s="18">
+        <v>13507</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>265</v>
@@ -2870,8 +3081,8 @@
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>44301</v>
+      <c r="A52" s="18">
+        <v>13507</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>34</v>
@@ -2890,8 +3101,8 @@
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>44301</v>
+      <c r="A53" s="18">
+        <v>13507</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>265</v>
@@ -2910,8 +3121,8 @@
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>44301</v>
+      <c r="A54" s="18">
+        <v>13507</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>140</v>
@@ -2930,8 +3141,8 @@
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>44301</v>
+      <c r="A55" s="18">
+        <v>13507</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>27</v>
@@ -2950,8 +3161,8 @@
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>44301</v>
+      <c r="A56" s="18">
+        <v>13507</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>34</v>
@@ -2970,8 +3181,8 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>44301</v>
+      <c r="A57" s="18">
+        <v>13507</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>125</v>
@@ -2996,8 +3207,8 @@
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>44101</v>
+      <c r="A58" s="18">
+        <v>13503</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>34</v>
@@ -3013,8 +3224,8 @@
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>44101</v>
+      <c r="A59" s="18">
+        <v>13503</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>27</v>
@@ -3033,8 +3244,8 @@
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>44001</v>
+      <c r="A60" s="18">
+        <v>13501</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>34</v>
@@ -3053,8 +3264,8 @@
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>44001</v>
+      <c r="A61" s="18">
+        <v>13501</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>27</v>
@@ -3074,8 +3285,8 @@
       </c>
     </row>
     <row r="62" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>380</v>
+      <c r="A62" s="18" t="s">
+        <v>378</v>
       </c>
       <c r="B62" s="13" t="s">
         <v>17</v>
@@ -3085,61 +3296,61 @@
       </c>
     </row>
     <row r="63" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>44102</v>
+      <c r="A63" s="18">
+        <v>13504</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L63" s="14" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>44102</v>
+      <c r="A64" s="18">
+        <v>13504</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>44102</v>
+      <c r="A65" s="18">
+        <v>13504</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="66" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>44102</v>
+      <c r="A66" s="18">
+        <v>13504</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>32</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="67" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>44102</v>
+      <c r="A67" s="18">
+        <v>13504</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>17</v>
@@ -3152,8 +3363,8 @@
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>44102</v>
+      <c r="A68" s="18">
+        <v>13504</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>158</v>
@@ -3169,8 +3380,8 @@
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>44102</v>
+      <c r="A69" s="18">
+        <v>13504</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>27</v>
@@ -3189,8 +3400,8 @@
       </c>
     </row>
     <row r="70" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>44102</v>
+      <c r="A70" s="18">
+        <v>13504</v>
       </c>
       <c r="B70" s="14" t="s">
         <v>32</v>
@@ -3200,8 +3411,8 @@
       </c>
     </row>
     <row r="71" spans="1:13" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>44102</v>
+      <c r="A71" s="18">
+        <v>13504</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>276</v>
@@ -3217,8 +3428,8 @@
       </c>
     </row>
     <row r="72" spans="1:13" s="14" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>44102</v>
+      <c r="A72" s="18">
+        <v>13504</v>
       </c>
       <c r="B72" s="14" t="s">
         <v>17</v>
@@ -3232,8 +3443,8 @@
       </c>
     </row>
     <row r="73" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>44102</v>
+      <c r="A73" s="18">
+        <v>13504</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>278</v>
@@ -3250,8 +3461,8 @@
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>44102</v>
+      <c r="A74" s="18">
+        <v>13504</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>24</v>
@@ -3265,8 +3476,8 @@
       </c>
     </row>
     <row r="75" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>44102</v>
+      <c r="A75" s="18">
+        <v>13504</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>276</v>
@@ -3275,12 +3486,12 @@
         <v>333</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>44102</v>
+      <c r="A76" s="18">
+        <v>13504</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>125</v>
@@ -3299,8 +3510,8 @@
       </c>
     </row>
     <row r="77" spans="1:13" ht="165" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>44102</v>
+      <c r="A77" s="18">
+        <v>13504</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>125</v>
@@ -3316,8 +3527,8 @@
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>44102</v>
+      <c r="A78" s="18">
+        <v>13504</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>24</v>
@@ -3330,8 +3541,8 @@
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>44102</v>
+      <c r="A79" s="18">
+        <v>13504</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>24</v>
@@ -3344,8 +3555,8 @@
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>44102</v>
+      <c r="A80" s="18">
+        <v>13504</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>24</v>
@@ -3354,20 +3565,20 @@
         <v>288</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="81" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>44102</v>
+      <c r="A81" s="18">
+        <v>13504</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>44102</v>
+      <c r="A82" s="18">
+        <v>13504</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>24</v>
@@ -3380,8 +3591,8 @@
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>44102</v>
+      <c r="A83" s="18">
+        <v>13504</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>24</v>
@@ -3394,8 +3605,8 @@
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>44102</v>
+      <c r="A84" s="18">
+        <v>13504</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>24</v>
@@ -3408,8 +3619,8 @@
       </c>
     </row>
     <row r="85" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>44102</v>
+      <c r="A85" s="18">
+        <v>13504</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>289</v>
@@ -3428,8 +3639,8 @@
       </c>
     </row>
     <row r="86" spans="1:12" s="14" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>44102</v>
+      <c r="A86" s="18">
+        <v>13504</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>32</v>
@@ -3440,26 +3651,26 @@
       <c r="D86" s="17"/>
     </row>
     <row r="87" spans="1:12" s="14" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>44103</v>
+      <c r="A87" s="18">
+        <v>13505</v>
       </c>
       <c r="B87" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C87" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D87" s="17"/>
       <c r="G87" s="14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L87" s="14" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>44103</v>
+      <c r="A88" s="18">
+        <v>13505</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>345</v>
@@ -3468,15 +3679,15 @@
         <v>344</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F88" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>44103</v>
+      <c r="A89" s="18">
+        <v>13505</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>125</v>
@@ -3495,8 +3706,8 @@
       </c>
     </row>
     <row r="90" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>44103</v>
+      <c r="A90" s="18">
+        <v>13505</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>125</v>
@@ -3515,8 +3726,8 @@
       </c>
     </row>
     <row r="91" spans="1:12" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>44103</v>
+      <c r="A91" s="18">
+        <v>13505</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>24</v>
@@ -3525,38 +3736,38 @@
         <v>352</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="92" spans="1:12" s="14" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>44103</v>
+      <c r="A92" s="18">
+        <v>13505</v>
       </c>
       <c r="B92" s="14" t="s">
         <v>32</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>44103</v>
+      <c r="A93" s="18">
+        <v>13505</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D93" s="8"/>
       <c r="J93" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="94" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>380</v>
+      <c r="A94" s="18" t="s">
+        <v>378</v>
       </c>
       <c r="B94" s="13" t="s">
         <v>32</v>
@@ -3565,99 +3776,123 @@
         <v>317</v>
       </c>
     </row>
-    <row r="95" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>44002</v>
-      </c>
-      <c r="B96" s="16" t="s">
+    <row r="95" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F96" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C96" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="L96" s="16" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>44002</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>44002</v>
+      <c r="C97" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="210" x14ac:dyDescent="0.25">
+      <c r="A98" s="18" t="s">
+        <v>379</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>357</v>
+        <v>35</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="F98" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>44002</v>
-      </c>
-      <c r="B99" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C99" s="16" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>44002</v>
-      </c>
-      <c r="B100" s="3" t="s">
+    <row r="99" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="B99" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C100" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="210" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>44002</v>
+      <c r="C99" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G99" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" s="18">
+        <v>13502</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F100" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A101" s="18">
+        <v>13502</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D101" s="8" t="s">
-        <v>36</v>
+        <v>187</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>37</v>
@@ -3666,92 +3901,104 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="13">
-        <v>10000</v>
-      </c>
-      <c r="B102" s="13" t="s">
+    <row r="102" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="18">
+        <v>13502</v>
+      </c>
+      <c r="B102" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C102" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G102" s="13" t="s">
-        <v>38</v>
+      <c r="C102" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="L102" s="16" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>44002</v>
+      <c r="A103" s="18">
+        <v>13502</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="F103" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>22</v>
+        <v>0</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>44002</v>
+      <c r="A104" s="18">
+        <v>13502</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>37</v>
+        <v>179</v>
       </c>
       <c r="F104" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>44002</v>
-      </c>
-      <c r="B105" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C105" s="16" t="s">
-        <v>375</v>
-      </c>
-      <c r="L105" s="16" t="s">
-        <v>332</v>
+        <v>0</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A105" s="18">
+        <v>13502</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <v>44002</v>
+      <c r="A106" s="18">
+        <v>13502</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F106" s="2" t="b">
         <v>0</v>
@@ -3761,20 +4008,20 @@
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>44002</v>
+      <c r="A107" s="18">
+        <v>13502</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="F107" s="2" t="b">
         <v>0</v>
@@ -3783,135 +4030,129 @@
         <v>251</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <v>44002</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="F108" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>251</v>
+    <row r="108" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="18">
+        <v>13502</v>
+      </c>
+      <c r="B108" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <v>44002</v>
+      <c r="A109" s="18">
+        <v>13506</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>125</v>
+        <v>34</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>183</v>
+        <v>37</v>
       </c>
       <c r="F109" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>251</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <v>44002</v>
+      <c r="A110" s="18">
+        <v>13506</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>196</v>
+        <v>240</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="F110" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <v>44002</v>
-      </c>
-      <c r="B111" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C111" s="16" t="s">
-        <v>375</v>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" s="18">
+        <v>13506</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F111" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <v>44104</v>
+      <c r="A112" s="18">
+        <v>13506</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F112" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="18">
+        <v>13506</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E112" s="2" t="s">
+      <c r="C113" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F112" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>44104</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="F113" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="G113" s="2" t="s">
-        <v>241</v>
-      </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <v>44104</v>
+      <c r="A114" s="18">
+        <v>13506</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>188</v>
@@ -3923,18 +4164,18 @@
         <v>1</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115">
-        <v>44104</v>
+      <c r="A115" s="18">
+        <v>13506</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>232</v>
@@ -3943,131 +4184,68 @@
         <v>1</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116">
-        <v>44104</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F116" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117">
-        <v>44104</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F117" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="B116" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C116" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118">
-        <v>44104</v>
+      <c r="A118" s="13">
+        <v>10000</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>254</v>
+        <v>303</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F118" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="13">
-        <v>10000</v>
-      </c>
-      <c r="B119" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C119" s="13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="13">
-        <v>10000</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="13">
-        <v>10000</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D121" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="200" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C200" s="2" t="s">
+    <row r="197" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C197" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="201" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="D201" s="2" t="s">
+    <row r="198" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D198" s="2" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:M121" xr:uid="{6D2A72A4-B69F-42B0-BA64-020C51FE6931}"/>
+  <autoFilter ref="B1:M118" xr:uid="{6D2A72A4-B69F-42B0-BA64-020C51FE6931}"/>
   <conditionalFormatting sqref="C8:C12">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C58:C59">
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C68:C69 C31 C71 C79:C86 C60:C61 C88:C93 C73:C77">
-    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C58:C59">
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D91">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -4076,7 +4254,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D63B81B-C0DE-4D5C-B8D8-1821B93262B2}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" style="2" customWidth="1"/>
@@ -4086,9 +4264,9 @@
     <col min="5" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>40</v>
@@ -4099,9 +4277,12 @@
       <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="E1" s="6" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="19">
         <v>10000</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -4114,8 +4295,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="19">
         <v>10000</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -4128,491 +4309,578 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>42002</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B6" t="s">
+        <v>381</v>
+      </c>
+      <c r="C6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" t="s">
+        <v>384</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B8" t="s">
+        <v>386</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B9" t="s">
+        <v>386</v>
+      </c>
+      <c r="C9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" t="s">
+        <v>384</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B10" t="s">
+        <v>386</v>
+      </c>
+      <c r="C10" t="s">
+        <v>387</v>
+      </c>
+      <c r="D10" t="s">
+        <v>388</v>
+      </c>
+      <c r="E10" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B11" t="s">
+        <v>390</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B12" t="s">
+        <v>390</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B13" t="s">
+        <v>390</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E13" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="C16" s="19">
+        <v>1</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="C17" s="19">
+        <v>2</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="C18" s="19">
+        <v>3</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="C19" s="19">
+        <v>4</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="C20" s="19">
+        <v>5</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="19">
+        <v>10000</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="18">
+        <v>13302</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C33" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D33" s="11" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>42002</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="18">
+        <v>13302</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C34" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D34" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J34" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>42002</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="18">
+        <v>13302</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C35" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D35" s="11" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>42002</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="18">
+        <v>13302</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C36" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D36" s="11" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>42002</v>
-      </c>
-      <c r="B8" s="3" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="18">
+        <v>13302</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C37" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D37" s="11" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>42002</v>
-      </c>
-      <c r="B9" s="3" t="s">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="18">
+        <v>13302</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>0</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>42002</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>42002</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>42002</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>42002</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>42002</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>42002</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>42002</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>42002</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>42002</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>42002</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>42002</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>42002</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>42002</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>42002</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>42002</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>42002</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>42002</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>42002</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>44301</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>44301</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>44301</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>44301</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>44301</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>44301</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>44102</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>44102</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>44102</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>44102</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>44102</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>41</v>
@@ -4621,166 +4889,166 @@
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>44104</v>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="18">
+        <v>13302</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>197</v>
+        <v>88</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>205</v>
+        <v>89</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>44104</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="18">
+        <v>13302</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>197</v>
+        <v>88</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>206</v>
+        <v>90</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>44104</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="18">
+        <v>13302</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>197</v>
+        <v>88</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>207</v>
+        <v>91</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>44104</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="18">
+        <v>13302</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>197</v>
+        <v>88</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>208</v>
+        <v>86</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>44104</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="18">
+        <v>13302</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C43" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="18">
+        <v>13302</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>44104</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>44104</v>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="18">
+        <v>13302</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>209</v>
+        <v>96</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>217</v>
+        <v>97</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>44104</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="18">
+        <v>13302</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>209</v>
+        <v>96</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>218</v>
+        <v>98</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>44104</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="18">
+        <v>13302</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>209</v>
+        <v>96</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>219</v>
+        <v>99</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>44104</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="18">
+        <v>13302</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>209</v>
+        <v>96</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>214</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>44104</v>
+      <c r="A49" s="18">
+        <v>13302</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>209</v>
+        <v>96</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>215</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>44104</v>
+      <c r="A50" s="18">
+        <v>13302</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>209</v>
+        <v>96</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>41</v>
@@ -4790,34 +5058,455 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>44103</v>
+      <c r="A51" s="18">
+        <v>13302</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="18">
+        <v>13302</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="18">
+        <v>13302</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="18">
+        <v>13302</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="18">
+        <v>13302</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="18">
+        <v>13302</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="18">
+        <v>13507</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="18">
+        <v>13507</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="18">
+        <v>13507</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="18">
+        <v>13507</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="18">
+        <v>13507</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="18">
+        <v>13507</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="18">
+        <v>13504</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="18">
+        <v>13504</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="18">
+        <v>13504</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="18">
+        <v>13504</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="18">
+        <v>13504</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="18">
+        <v>13506</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="18">
+        <v>13506</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="18">
+        <v>13506</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="18">
+        <v>13506</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="18">
+        <v>13506</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="18">
+        <v>13506</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="18">
+        <v>13506</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="18">
+        <v>13506</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="18">
+        <v>13506</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="18">
+        <v>13506</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="18">
+        <v>13506</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="18">
+        <v>13506</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="18">
+        <v>13505</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C80" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D80" s="2" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>44103</v>
-      </c>
-      <c r="B52" s="2" t="s">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="18">
+        <v>13505</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C81" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D81" s="2" t="s">
         <v>342</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C4:C6">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:C10">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C12">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:C20">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21:C32">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -4870,6 +5559,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE51FB2AFBB2DD429D3D11FE759FFC43" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1354c8e90e28409d311bbba5db8dc335">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4877444-78fa-4cfa-bafc-d6c64fafc061" xmlns:ns3="d0fa6634-326e-4532-91a2-52bea7ac9212" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbb4473bd7833dc3543803a005841490" ns2:_="" ns3:_="">
     <xsd:import namespace="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
@@ -5110,15 +5808,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A28B40-7C99-42AA-A812-F7E1B312E52E}">
   <ds:schemaRefs>
@@ -5133,6 +5822,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD810D2-AE12-44E9-9666-8142EEC15392}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D17A2946-34CC-446E-B90E-BB649BEB931E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5149,12 +5846,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD810D2-AE12-44E9-9666-8142EEC15392}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>